--- a/websites.xlsx
+++ b/websites.xlsx
@@ -713,7 +713,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>//*[@id="blurb_rail_copy_copy"]/div/div/div/div/div/div[1]/div/div/div[1]/div[2]/div[1]</t>
+          <t>//*[@id="pricing_bar_copy"]//ins</t>
         </is>
       </c>
     </row>
